--- a/public/fixcar_car_template.xlsx
+++ b/public/fixcar_car_template.xlsx
@@ -79,14 +79,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F6FF"/>
-        <bgColor rgb="00F0F6FF"/>
+        <fgColor rgb="00FFFFF0"/>
+        <bgColor rgb="00FFFFF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFF0"/>
-        <bgColor rgb="00FFFFF0"/>
+        <fgColor rgb="00F0F6FF"/>
+        <bgColor rgb="00F0F6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,10 +124,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:AM52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -511,25 +511,39 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="50" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -595,7 +609,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>사고여부</t>
+          <t>사고여부 *</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -625,37 +639,107 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>매매유형</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>압류</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>저당</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>사고이력공개</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>설명글</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>옵션 (콤마구분)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>메인사진1 URL</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>메인사진2 URL</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>메인사진3 URL</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>메인사진4 URL</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>실내사진 URL</t>
+          <t>리스종류</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>리스사</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>리스기간 시작</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>리스기간 종료</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>월리스료(만원)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>리스 보증금(만원)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>리스 잔존가치(만원)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>리스 인수정산금(만원)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>렌트사</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>렌트기간 시작</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>렌트기간 종료</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>월렌트료(만원)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>렌트 보증금(만원)</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>렌트 잔존가치(만원)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>렌트 인수정산금(만원)</t>
         </is>
       </c>
     </row>
@@ -742,7 +826,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>일반차량/리스승계/렌트</t>
+          <t>일반차량/리스승계차량/렌트차량</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -752,37 +836,107 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
+          <t>직접매도/매매알선</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>없음/있음</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>없음/있음</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>공개/비공개</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
           <t>차량 상태, 특이사항 등</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>예: 선루프,후방카메라,열선시트</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Cloudinary URL</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>Cloudinary URL</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>Cloudinary URL</t>
-        </is>
-      </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>Cloudinary URL</t>
-        </is>
-      </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>Cloudinary URL</t>
+          <t>운용리스/금융리스 (리스승계시)</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>예: 현대캐피탈</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>예: 2023-01</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>예: 2026-01</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>예: 50</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>예: 500</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>예: 1000</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>예: 200</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="inlineStr">
+        <is>
+          <t>예: 롯데렌탈 (렌트시)</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>예: 2023-01</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>예: 2026-01</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
+          <t>예: 40</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="inlineStr">
+        <is>
+          <t>예: 300</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>예: 800</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>예: 150</t>
         </is>
       </c>
     </row>
@@ -879,19 +1033,49 @@
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
+          <t>직접매도</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>비공개</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
           <t>1인 소유 비흡연 차량입니다.</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>선루프,후방카메라,열선시트,스마트키,네비게이션</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="n"/>
-      <c r="V3" s="5" t="n"/>
-      <c r="W3" s="5" t="n"/>
-      <c r="X3" s="5" t="n"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>선루프,후방카메라,열선시트,스마트키</t>
+        </is>
+      </c>
       <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n"/>
+      <c r="AB3" s="5" t="n"/>
+      <c r="AC3" s="5" t="n"/>
+      <c r="AD3" s="5" t="n"/>
+      <c r="AE3" s="5" t="n"/>
+      <c r="AF3" s="5" t="n"/>
+      <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="5" t="n"/>
+      <c r="AI3" s="5" t="n"/>
+      <c r="AJ3" s="5" t="n"/>
+      <c r="AK3" s="5" t="n"/>
+      <c r="AL3" s="5" t="n"/>
+      <c r="AM3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -919,6 +1103,20 @@
       <c r="W4" s="5" t="n"/>
       <c r="X4" s="5" t="n"/>
       <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+      <c r="AI4" s="5" t="n"/>
+      <c r="AJ4" s="5" t="n"/>
+      <c r="AK4" s="5" t="n"/>
+      <c r="AL4" s="5" t="n"/>
+      <c r="AM4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -946,6 +1144,20 @@
       <c r="W5" s="5" t="n"/>
       <c r="X5" s="5" t="n"/>
       <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+      <c r="AI5" s="5" t="n"/>
+      <c r="AJ5" s="5" t="n"/>
+      <c r="AK5" s="5" t="n"/>
+      <c r="AL5" s="5" t="n"/>
+      <c r="AM5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -973,6 +1185,20 @@
       <c r="W6" s="5" t="n"/>
       <c r="X6" s="5" t="n"/>
       <c r="Y6" s="5" t="n"/>
+      <c r="Z6" s="5" t="n"/>
+      <c r="AA6" s="5" t="n"/>
+      <c r="AB6" s="5" t="n"/>
+      <c r="AC6" s="5" t="n"/>
+      <c r="AD6" s="5" t="n"/>
+      <c r="AE6" s="5" t="n"/>
+      <c r="AF6" s="5" t="n"/>
+      <c r="AG6" s="5" t="n"/>
+      <c r="AH6" s="5" t="n"/>
+      <c r="AI6" s="5" t="n"/>
+      <c r="AJ6" s="5" t="n"/>
+      <c r="AK6" s="5" t="n"/>
+      <c r="AL6" s="5" t="n"/>
+      <c r="AM6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1000,6 +1226,20 @@
       <c r="W7" s="5" t="n"/>
       <c r="X7" s="5" t="n"/>
       <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" s="5" t="n"/>
+      <c r="AB7" s="5" t="n"/>
+      <c r="AC7" s="5" t="n"/>
+      <c r="AD7" s="5" t="n"/>
+      <c r="AE7" s="5" t="n"/>
+      <c r="AF7" s="5" t="n"/>
+      <c r="AG7" s="5" t="n"/>
+      <c r="AH7" s="5" t="n"/>
+      <c r="AI7" s="5" t="n"/>
+      <c r="AJ7" s="5" t="n"/>
+      <c r="AK7" s="5" t="n"/>
+      <c r="AL7" s="5" t="n"/>
+      <c r="AM7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1027,6 +1267,20 @@
       <c r="W8" s="5" t="n"/>
       <c r="X8" s="5" t="n"/>
       <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="5" t="n"/>
+      <c r="AA8" s="5" t="n"/>
+      <c r="AB8" s="5" t="n"/>
+      <c r="AC8" s="5" t="n"/>
+      <c r="AD8" s="5" t="n"/>
+      <c r="AE8" s="5" t="n"/>
+      <c r="AF8" s="5" t="n"/>
+      <c r="AG8" s="5" t="n"/>
+      <c r="AH8" s="5" t="n"/>
+      <c r="AI8" s="5" t="n"/>
+      <c r="AJ8" s="5" t="n"/>
+      <c r="AK8" s="5" t="n"/>
+      <c r="AL8" s="5" t="n"/>
+      <c r="AM8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1054,6 +1308,20 @@
       <c r="W9" s="5" t="n"/>
       <c r="X9" s="5" t="n"/>
       <c r="Y9" s="5" t="n"/>
+      <c r="Z9" s="5" t="n"/>
+      <c r="AA9" s="5" t="n"/>
+      <c r="AB9" s="5" t="n"/>
+      <c r="AC9" s="5" t="n"/>
+      <c r="AD9" s="5" t="n"/>
+      <c r="AE9" s="5" t="n"/>
+      <c r="AF9" s="5" t="n"/>
+      <c r="AG9" s="5" t="n"/>
+      <c r="AH9" s="5" t="n"/>
+      <c r="AI9" s="5" t="n"/>
+      <c r="AJ9" s="5" t="n"/>
+      <c r="AK9" s="5" t="n"/>
+      <c r="AL9" s="5" t="n"/>
+      <c r="AM9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1081,6 +1349,20 @@
       <c r="W10" s="5" t="n"/>
       <c r="X10" s="5" t="n"/>
       <c r="Y10" s="5" t="n"/>
+      <c r="Z10" s="5" t="n"/>
+      <c r="AA10" s="5" t="n"/>
+      <c r="AB10" s="5" t="n"/>
+      <c r="AC10" s="5" t="n"/>
+      <c r="AD10" s="5" t="n"/>
+      <c r="AE10" s="5" t="n"/>
+      <c r="AF10" s="5" t="n"/>
+      <c r="AG10" s="5" t="n"/>
+      <c r="AH10" s="5" t="n"/>
+      <c r="AI10" s="5" t="n"/>
+      <c r="AJ10" s="5" t="n"/>
+      <c r="AK10" s="5" t="n"/>
+      <c r="AL10" s="5" t="n"/>
+      <c r="AM10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1108,6 +1390,20 @@
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
       <c r="Y11" s="5" t="n"/>
+      <c r="Z11" s="5" t="n"/>
+      <c r="AA11" s="5" t="n"/>
+      <c r="AB11" s="5" t="n"/>
+      <c r="AC11" s="5" t="n"/>
+      <c r="AD11" s="5" t="n"/>
+      <c r="AE11" s="5" t="n"/>
+      <c r="AF11" s="5" t="n"/>
+      <c r="AG11" s="5" t="n"/>
+      <c r="AH11" s="5" t="n"/>
+      <c r="AI11" s="5" t="n"/>
+      <c r="AJ11" s="5" t="n"/>
+      <c r="AK11" s="5" t="n"/>
+      <c r="AL11" s="5" t="n"/>
+      <c r="AM11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1135,6 +1431,20 @@
       <c r="W12" s="5" t="n"/>
       <c r="X12" s="5" t="n"/>
       <c r="Y12" s="5" t="n"/>
+      <c r="Z12" s="5" t="n"/>
+      <c r="AA12" s="5" t="n"/>
+      <c r="AB12" s="5" t="n"/>
+      <c r="AC12" s="5" t="n"/>
+      <c r="AD12" s="5" t="n"/>
+      <c r="AE12" s="5" t="n"/>
+      <c r="AF12" s="5" t="n"/>
+      <c r="AG12" s="5" t="n"/>
+      <c r="AH12" s="5" t="n"/>
+      <c r="AI12" s="5" t="n"/>
+      <c r="AJ12" s="5" t="n"/>
+      <c r="AK12" s="5" t="n"/>
+      <c r="AL12" s="5" t="n"/>
+      <c r="AM12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1162,6 +1472,20 @@
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
       <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="5" t="n"/>
+      <c r="AA13" s="5" t="n"/>
+      <c r="AB13" s="5" t="n"/>
+      <c r="AC13" s="5" t="n"/>
+      <c r="AD13" s="5" t="n"/>
+      <c r="AE13" s="5" t="n"/>
+      <c r="AF13" s="5" t="n"/>
+      <c r="AG13" s="5" t="n"/>
+      <c r="AH13" s="5" t="n"/>
+      <c r="AI13" s="5" t="n"/>
+      <c r="AJ13" s="5" t="n"/>
+      <c r="AK13" s="5" t="n"/>
+      <c r="AL13" s="5" t="n"/>
+      <c r="AM13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1189,6 +1513,20 @@
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
       <c r="Y14" s="5" t="n"/>
+      <c r="Z14" s="5" t="n"/>
+      <c r="AA14" s="5" t="n"/>
+      <c r="AB14" s="5" t="n"/>
+      <c r="AC14" s="5" t="n"/>
+      <c r="AD14" s="5" t="n"/>
+      <c r="AE14" s="5" t="n"/>
+      <c r="AF14" s="5" t="n"/>
+      <c r="AG14" s="5" t="n"/>
+      <c r="AH14" s="5" t="n"/>
+      <c r="AI14" s="5" t="n"/>
+      <c r="AJ14" s="5" t="n"/>
+      <c r="AK14" s="5" t="n"/>
+      <c r="AL14" s="5" t="n"/>
+      <c r="AM14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1216,6 +1554,20 @@
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
       <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="5" t="n"/>
+      <c r="AA15" s="5" t="n"/>
+      <c r="AB15" s="5" t="n"/>
+      <c r="AC15" s="5" t="n"/>
+      <c r="AD15" s="5" t="n"/>
+      <c r="AE15" s="5" t="n"/>
+      <c r="AF15" s="5" t="n"/>
+      <c r="AG15" s="5" t="n"/>
+      <c r="AH15" s="5" t="n"/>
+      <c r="AI15" s="5" t="n"/>
+      <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="5" t="n"/>
+      <c r="AL15" s="5" t="n"/>
+      <c r="AM15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1243,6 +1595,20 @@
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
       <c r="Y16" s="5" t="n"/>
+      <c r="Z16" s="5" t="n"/>
+      <c r="AA16" s="5" t="n"/>
+      <c r="AB16" s="5" t="n"/>
+      <c r="AC16" s="5" t="n"/>
+      <c r="AD16" s="5" t="n"/>
+      <c r="AE16" s="5" t="n"/>
+      <c r="AF16" s="5" t="n"/>
+      <c r="AG16" s="5" t="n"/>
+      <c r="AH16" s="5" t="n"/>
+      <c r="AI16" s="5" t="n"/>
+      <c r="AJ16" s="5" t="n"/>
+      <c r="AK16" s="5" t="n"/>
+      <c r="AL16" s="5" t="n"/>
+      <c r="AM16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1270,6 +1636,20 @@
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
       <c r="Y17" s="5" t="n"/>
+      <c r="Z17" s="5" t="n"/>
+      <c r="AA17" s="5" t="n"/>
+      <c r="AB17" s="5" t="n"/>
+      <c r="AC17" s="5" t="n"/>
+      <c r="AD17" s="5" t="n"/>
+      <c r="AE17" s="5" t="n"/>
+      <c r="AF17" s="5" t="n"/>
+      <c r="AG17" s="5" t="n"/>
+      <c r="AH17" s="5" t="n"/>
+      <c r="AI17" s="5" t="n"/>
+      <c r="AJ17" s="5" t="n"/>
+      <c r="AK17" s="5" t="n"/>
+      <c r="AL17" s="5" t="n"/>
+      <c r="AM17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1297,6 +1677,20 @@
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
       <c r="Y18" s="5" t="n"/>
+      <c r="Z18" s="5" t="n"/>
+      <c r="AA18" s="5" t="n"/>
+      <c r="AB18" s="5" t="n"/>
+      <c r="AC18" s="5" t="n"/>
+      <c r="AD18" s="5" t="n"/>
+      <c r="AE18" s="5" t="n"/>
+      <c r="AF18" s="5" t="n"/>
+      <c r="AG18" s="5" t="n"/>
+      <c r="AH18" s="5" t="n"/>
+      <c r="AI18" s="5" t="n"/>
+      <c r="AJ18" s="5" t="n"/>
+      <c r="AK18" s="5" t="n"/>
+      <c r="AL18" s="5" t="n"/>
+      <c r="AM18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1324,6 +1718,20 @@
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
       <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+      <c r="AA19" s="5" t="n"/>
+      <c r="AB19" s="5" t="n"/>
+      <c r="AC19" s="5" t="n"/>
+      <c r="AD19" s="5" t="n"/>
+      <c r="AE19" s="5" t="n"/>
+      <c r="AF19" s="5" t="n"/>
+      <c r="AG19" s="5" t="n"/>
+      <c r="AH19" s="5" t="n"/>
+      <c r="AI19" s="5" t="n"/>
+      <c r="AJ19" s="5" t="n"/>
+      <c r="AK19" s="5" t="n"/>
+      <c r="AL19" s="5" t="n"/>
+      <c r="AM19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1351,6 +1759,20 @@
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
       <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="5" t="n"/>
+      <c r="AA20" s="5" t="n"/>
+      <c r="AB20" s="5" t="n"/>
+      <c r="AC20" s="5" t="n"/>
+      <c r="AD20" s="5" t="n"/>
+      <c r="AE20" s="5" t="n"/>
+      <c r="AF20" s="5" t="n"/>
+      <c r="AG20" s="5" t="n"/>
+      <c r="AH20" s="5" t="n"/>
+      <c r="AI20" s="5" t="n"/>
+      <c r="AJ20" s="5" t="n"/>
+      <c r="AK20" s="5" t="n"/>
+      <c r="AL20" s="5" t="n"/>
+      <c r="AM20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1378,6 +1800,20 @@
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
       <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="n"/>
+      <c r="AB21" s="5" t="n"/>
+      <c r="AC21" s="5" t="n"/>
+      <c r="AD21" s="5" t="n"/>
+      <c r="AE21" s="5" t="n"/>
+      <c r="AF21" s="5" t="n"/>
+      <c r="AG21" s="5" t="n"/>
+      <c r="AH21" s="5" t="n"/>
+      <c r="AI21" s="5" t="n"/>
+      <c r="AJ21" s="5" t="n"/>
+      <c r="AK21" s="5" t="n"/>
+      <c r="AL21" s="5" t="n"/>
+      <c r="AM21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1405,6 +1841,20 @@
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
       <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5" t="n"/>
+      <c r="AA22" s="5" t="n"/>
+      <c r="AB22" s="5" t="n"/>
+      <c r="AC22" s="5" t="n"/>
+      <c r="AD22" s="5" t="n"/>
+      <c r="AE22" s="5" t="n"/>
+      <c r="AF22" s="5" t="n"/>
+      <c r="AG22" s="5" t="n"/>
+      <c r="AH22" s="5" t="n"/>
+      <c r="AI22" s="5" t="n"/>
+      <c r="AJ22" s="5" t="n"/>
+      <c r="AK22" s="5" t="n"/>
+      <c r="AL22" s="5" t="n"/>
+      <c r="AM22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1432,6 +1882,20 @@
       <c r="W23" s="5" t="n"/>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="5" t="n"/>
+      <c r="Z23" s="5" t="n"/>
+      <c r="AA23" s="5" t="n"/>
+      <c r="AB23" s="5" t="n"/>
+      <c r="AC23" s="5" t="n"/>
+      <c r="AD23" s="5" t="n"/>
+      <c r="AE23" s="5" t="n"/>
+      <c r="AF23" s="5" t="n"/>
+      <c r="AG23" s="5" t="n"/>
+      <c r="AH23" s="5" t="n"/>
+      <c r="AI23" s="5" t="n"/>
+      <c r="AJ23" s="5" t="n"/>
+      <c r="AK23" s="5" t="n"/>
+      <c r="AL23" s="5" t="n"/>
+      <c r="AM23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1459,6 +1923,20 @@
       <c r="W24" s="5" t="n"/>
       <c r="X24" s="5" t="n"/>
       <c r="Y24" s="5" t="n"/>
+      <c r="Z24" s="5" t="n"/>
+      <c r="AA24" s="5" t="n"/>
+      <c r="AB24" s="5" t="n"/>
+      <c r="AC24" s="5" t="n"/>
+      <c r="AD24" s="5" t="n"/>
+      <c r="AE24" s="5" t="n"/>
+      <c r="AF24" s="5" t="n"/>
+      <c r="AG24" s="5" t="n"/>
+      <c r="AH24" s="5" t="n"/>
+      <c r="AI24" s="5" t="n"/>
+      <c r="AJ24" s="5" t="n"/>
+      <c r="AK24" s="5" t="n"/>
+      <c r="AL24" s="5" t="n"/>
+      <c r="AM24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1486,6 +1964,20 @@
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
       <c r="Y25" s="5" t="n"/>
+      <c r="Z25" s="5" t="n"/>
+      <c r="AA25" s="5" t="n"/>
+      <c r="AB25" s="5" t="n"/>
+      <c r="AC25" s="5" t="n"/>
+      <c r="AD25" s="5" t="n"/>
+      <c r="AE25" s="5" t="n"/>
+      <c r="AF25" s="5" t="n"/>
+      <c r="AG25" s="5" t="n"/>
+      <c r="AH25" s="5" t="n"/>
+      <c r="AI25" s="5" t="n"/>
+      <c r="AJ25" s="5" t="n"/>
+      <c r="AK25" s="5" t="n"/>
+      <c r="AL25" s="5" t="n"/>
+      <c r="AM25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1513,6 +2005,20 @@
       <c r="W26" s="5" t="n"/>
       <c r="X26" s="5" t="n"/>
       <c r="Y26" s="5" t="n"/>
+      <c r="Z26" s="5" t="n"/>
+      <c r="AA26" s="5" t="n"/>
+      <c r="AB26" s="5" t="n"/>
+      <c r="AC26" s="5" t="n"/>
+      <c r="AD26" s="5" t="n"/>
+      <c r="AE26" s="5" t="n"/>
+      <c r="AF26" s="5" t="n"/>
+      <c r="AG26" s="5" t="n"/>
+      <c r="AH26" s="5" t="n"/>
+      <c r="AI26" s="5" t="n"/>
+      <c r="AJ26" s="5" t="n"/>
+      <c r="AK26" s="5" t="n"/>
+      <c r="AL26" s="5" t="n"/>
+      <c r="AM26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1540,6 +2046,20 @@
       <c r="W27" s="5" t="n"/>
       <c r="X27" s="5" t="n"/>
       <c r="Y27" s="5" t="n"/>
+      <c r="Z27" s="5" t="n"/>
+      <c r="AA27" s="5" t="n"/>
+      <c r="AB27" s="5" t="n"/>
+      <c r="AC27" s="5" t="n"/>
+      <c r="AD27" s="5" t="n"/>
+      <c r="AE27" s="5" t="n"/>
+      <c r="AF27" s="5" t="n"/>
+      <c r="AG27" s="5" t="n"/>
+      <c r="AH27" s="5" t="n"/>
+      <c r="AI27" s="5" t="n"/>
+      <c r="AJ27" s="5" t="n"/>
+      <c r="AK27" s="5" t="n"/>
+      <c r="AL27" s="5" t="n"/>
+      <c r="AM27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1567,6 +2087,20 @@
       <c r="W28" s="5" t="n"/>
       <c r="X28" s="5" t="n"/>
       <c r="Y28" s="5" t="n"/>
+      <c r="Z28" s="5" t="n"/>
+      <c r="AA28" s="5" t="n"/>
+      <c r="AB28" s="5" t="n"/>
+      <c r="AC28" s="5" t="n"/>
+      <c r="AD28" s="5" t="n"/>
+      <c r="AE28" s="5" t="n"/>
+      <c r="AF28" s="5" t="n"/>
+      <c r="AG28" s="5" t="n"/>
+      <c r="AH28" s="5" t="n"/>
+      <c r="AI28" s="5" t="n"/>
+      <c r="AJ28" s="5" t="n"/>
+      <c r="AK28" s="5" t="n"/>
+      <c r="AL28" s="5" t="n"/>
+      <c r="AM28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1594,6 +2128,20 @@
       <c r="W29" s="5" t="n"/>
       <c r="X29" s="5" t="n"/>
       <c r="Y29" s="5" t="n"/>
+      <c r="Z29" s="5" t="n"/>
+      <c r="AA29" s="5" t="n"/>
+      <c r="AB29" s="5" t="n"/>
+      <c r="AC29" s="5" t="n"/>
+      <c r="AD29" s="5" t="n"/>
+      <c r="AE29" s="5" t="n"/>
+      <c r="AF29" s="5" t="n"/>
+      <c r="AG29" s="5" t="n"/>
+      <c r="AH29" s="5" t="n"/>
+      <c r="AI29" s="5" t="n"/>
+      <c r="AJ29" s="5" t="n"/>
+      <c r="AK29" s="5" t="n"/>
+      <c r="AL29" s="5" t="n"/>
+      <c r="AM29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1621,6 +2169,20 @@
       <c r="W30" s="5" t="n"/>
       <c r="X30" s="5" t="n"/>
       <c r="Y30" s="5" t="n"/>
+      <c r="Z30" s="5" t="n"/>
+      <c r="AA30" s="5" t="n"/>
+      <c r="AB30" s="5" t="n"/>
+      <c r="AC30" s="5" t="n"/>
+      <c r="AD30" s="5" t="n"/>
+      <c r="AE30" s="5" t="n"/>
+      <c r="AF30" s="5" t="n"/>
+      <c r="AG30" s="5" t="n"/>
+      <c r="AH30" s="5" t="n"/>
+      <c r="AI30" s="5" t="n"/>
+      <c r="AJ30" s="5" t="n"/>
+      <c r="AK30" s="5" t="n"/>
+      <c r="AL30" s="5" t="n"/>
+      <c r="AM30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1648,6 +2210,20 @@
       <c r="W31" s="5" t="n"/>
       <c r="X31" s="5" t="n"/>
       <c r="Y31" s="5" t="n"/>
+      <c r="Z31" s="5" t="n"/>
+      <c r="AA31" s="5" t="n"/>
+      <c r="AB31" s="5" t="n"/>
+      <c r="AC31" s="5" t="n"/>
+      <c r="AD31" s="5" t="n"/>
+      <c r="AE31" s="5" t="n"/>
+      <c r="AF31" s="5" t="n"/>
+      <c r="AG31" s="5" t="n"/>
+      <c r="AH31" s="5" t="n"/>
+      <c r="AI31" s="5" t="n"/>
+      <c r="AJ31" s="5" t="n"/>
+      <c r="AK31" s="5" t="n"/>
+      <c r="AL31" s="5" t="n"/>
+      <c r="AM31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1675,6 +2251,20 @@
       <c r="W32" s="5" t="n"/>
       <c r="X32" s="5" t="n"/>
       <c r="Y32" s="5" t="n"/>
+      <c r="Z32" s="5" t="n"/>
+      <c r="AA32" s="5" t="n"/>
+      <c r="AB32" s="5" t="n"/>
+      <c r="AC32" s="5" t="n"/>
+      <c r="AD32" s="5" t="n"/>
+      <c r="AE32" s="5" t="n"/>
+      <c r="AF32" s="5" t="n"/>
+      <c r="AG32" s="5" t="n"/>
+      <c r="AH32" s="5" t="n"/>
+      <c r="AI32" s="5" t="n"/>
+      <c r="AJ32" s="5" t="n"/>
+      <c r="AK32" s="5" t="n"/>
+      <c r="AL32" s="5" t="n"/>
+      <c r="AM32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1702,6 +2292,20 @@
       <c r="W33" s="5" t="n"/>
       <c r="X33" s="5" t="n"/>
       <c r="Y33" s="5" t="n"/>
+      <c r="Z33" s="5" t="n"/>
+      <c r="AA33" s="5" t="n"/>
+      <c r="AB33" s="5" t="n"/>
+      <c r="AC33" s="5" t="n"/>
+      <c r="AD33" s="5" t="n"/>
+      <c r="AE33" s="5" t="n"/>
+      <c r="AF33" s="5" t="n"/>
+      <c r="AG33" s="5" t="n"/>
+      <c r="AH33" s="5" t="n"/>
+      <c r="AI33" s="5" t="n"/>
+      <c r="AJ33" s="5" t="n"/>
+      <c r="AK33" s="5" t="n"/>
+      <c r="AL33" s="5" t="n"/>
+      <c r="AM33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1729,6 +2333,20 @@
       <c r="W34" s="5" t="n"/>
       <c r="X34" s="5" t="n"/>
       <c r="Y34" s="5" t="n"/>
+      <c r="Z34" s="5" t="n"/>
+      <c r="AA34" s="5" t="n"/>
+      <c r="AB34" s="5" t="n"/>
+      <c r="AC34" s="5" t="n"/>
+      <c r="AD34" s="5" t="n"/>
+      <c r="AE34" s="5" t="n"/>
+      <c r="AF34" s="5" t="n"/>
+      <c r="AG34" s="5" t="n"/>
+      <c r="AH34" s="5" t="n"/>
+      <c r="AI34" s="5" t="n"/>
+      <c r="AJ34" s="5" t="n"/>
+      <c r="AK34" s="5" t="n"/>
+      <c r="AL34" s="5" t="n"/>
+      <c r="AM34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1756,6 +2374,20 @@
       <c r="W35" s="5" t="n"/>
       <c r="X35" s="5" t="n"/>
       <c r="Y35" s="5" t="n"/>
+      <c r="Z35" s="5" t="n"/>
+      <c r="AA35" s="5" t="n"/>
+      <c r="AB35" s="5" t="n"/>
+      <c r="AC35" s="5" t="n"/>
+      <c r="AD35" s="5" t="n"/>
+      <c r="AE35" s="5" t="n"/>
+      <c r="AF35" s="5" t="n"/>
+      <c r="AG35" s="5" t="n"/>
+      <c r="AH35" s="5" t="n"/>
+      <c r="AI35" s="5" t="n"/>
+      <c r="AJ35" s="5" t="n"/>
+      <c r="AK35" s="5" t="n"/>
+      <c r="AL35" s="5" t="n"/>
+      <c r="AM35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1783,6 +2415,20 @@
       <c r="W36" s="5" t="n"/>
       <c r="X36" s="5" t="n"/>
       <c r="Y36" s="5" t="n"/>
+      <c r="Z36" s="5" t="n"/>
+      <c r="AA36" s="5" t="n"/>
+      <c r="AB36" s="5" t="n"/>
+      <c r="AC36" s="5" t="n"/>
+      <c r="AD36" s="5" t="n"/>
+      <c r="AE36" s="5" t="n"/>
+      <c r="AF36" s="5" t="n"/>
+      <c r="AG36" s="5" t="n"/>
+      <c r="AH36" s="5" t="n"/>
+      <c r="AI36" s="5" t="n"/>
+      <c r="AJ36" s="5" t="n"/>
+      <c r="AK36" s="5" t="n"/>
+      <c r="AL36" s="5" t="n"/>
+      <c r="AM36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1810,6 +2456,20 @@
       <c r="W37" s="5" t="n"/>
       <c r="X37" s="5" t="n"/>
       <c r="Y37" s="5" t="n"/>
+      <c r="Z37" s="5" t="n"/>
+      <c r="AA37" s="5" t="n"/>
+      <c r="AB37" s="5" t="n"/>
+      <c r="AC37" s="5" t="n"/>
+      <c r="AD37" s="5" t="n"/>
+      <c r="AE37" s="5" t="n"/>
+      <c r="AF37" s="5" t="n"/>
+      <c r="AG37" s="5" t="n"/>
+      <c r="AH37" s="5" t="n"/>
+      <c r="AI37" s="5" t="n"/>
+      <c r="AJ37" s="5" t="n"/>
+      <c r="AK37" s="5" t="n"/>
+      <c r="AL37" s="5" t="n"/>
+      <c r="AM37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1837,6 +2497,20 @@
       <c r="W38" s="5" t="n"/>
       <c r="X38" s="5" t="n"/>
       <c r="Y38" s="5" t="n"/>
+      <c r="Z38" s="5" t="n"/>
+      <c r="AA38" s="5" t="n"/>
+      <c r="AB38" s="5" t="n"/>
+      <c r="AC38" s="5" t="n"/>
+      <c r="AD38" s="5" t="n"/>
+      <c r="AE38" s="5" t="n"/>
+      <c r="AF38" s="5" t="n"/>
+      <c r="AG38" s="5" t="n"/>
+      <c r="AH38" s="5" t="n"/>
+      <c r="AI38" s="5" t="n"/>
+      <c r="AJ38" s="5" t="n"/>
+      <c r="AK38" s="5" t="n"/>
+      <c r="AL38" s="5" t="n"/>
+      <c r="AM38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1864,6 +2538,20 @@
       <c r="W39" s="5" t="n"/>
       <c r="X39" s="5" t="n"/>
       <c r="Y39" s="5" t="n"/>
+      <c r="Z39" s="5" t="n"/>
+      <c r="AA39" s="5" t="n"/>
+      <c r="AB39" s="5" t="n"/>
+      <c r="AC39" s="5" t="n"/>
+      <c r="AD39" s="5" t="n"/>
+      <c r="AE39" s="5" t="n"/>
+      <c r="AF39" s="5" t="n"/>
+      <c r="AG39" s="5" t="n"/>
+      <c r="AH39" s="5" t="n"/>
+      <c r="AI39" s="5" t="n"/>
+      <c r="AJ39" s="5" t="n"/>
+      <c r="AK39" s="5" t="n"/>
+      <c r="AL39" s="5" t="n"/>
+      <c r="AM39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1891,6 +2579,20 @@
       <c r="W40" s="5" t="n"/>
       <c r="X40" s="5" t="n"/>
       <c r="Y40" s="5" t="n"/>
+      <c r="Z40" s="5" t="n"/>
+      <c r="AA40" s="5" t="n"/>
+      <c r="AB40" s="5" t="n"/>
+      <c r="AC40" s="5" t="n"/>
+      <c r="AD40" s="5" t="n"/>
+      <c r="AE40" s="5" t="n"/>
+      <c r="AF40" s="5" t="n"/>
+      <c r="AG40" s="5" t="n"/>
+      <c r="AH40" s="5" t="n"/>
+      <c r="AI40" s="5" t="n"/>
+      <c r="AJ40" s="5" t="n"/>
+      <c r="AK40" s="5" t="n"/>
+      <c r="AL40" s="5" t="n"/>
+      <c r="AM40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1918,6 +2620,20 @@
       <c r="W41" s="5" t="n"/>
       <c r="X41" s="5" t="n"/>
       <c r="Y41" s="5" t="n"/>
+      <c r="Z41" s="5" t="n"/>
+      <c r="AA41" s="5" t="n"/>
+      <c r="AB41" s="5" t="n"/>
+      <c r="AC41" s="5" t="n"/>
+      <c r="AD41" s="5" t="n"/>
+      <c r="AE41" s="5" t="n"/>
+      <c r="AF41" s="5" t="n"/>
+      <c r="AG41" s="5" t="n"/>
+      <c r="AH41" s="5" t="n"/>
+      <c r="AI41" s="5" t="n"/>
+      <c r="AJ41" s="5" t="n"/>
+      <c r="AK41" s="5" t="n"/>
+      <c r="AL41" s="5" t="n"/>
+      <c r="AM41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1945,6 +2661,20 @@
       <c r="W42" s="5" t="n"/>
       <c r="X42" s="5" t="n"/>
       <c r="Y42" s="5" t="n"/>
+      <c r="Z42" s="5" t="n"/>
+      <c r="AA42" s="5" t="n"/>
+      <c r="AB42" s="5" t="n"/>
+      <c r="AC42" s="5" t="n"/>
+      <c r="AD42" s="5" t="n"/>
+      <c r="AE42" s="5" t="n"/>
+      <c r="AF42" s="5" t="n"/>
+      <c r="AG42" s="5" t="n"/>
+      <c r="AH42" s="5" t="n"/>
+      <c r="AI42" s="5" t="n"/>
+      <c r="AJ42" s="5" t="n"/>
+      <c r="AK42" s="5" t="n"/>
+      <c r="AL42" s="5" t="n"/>
+      <c r="AM42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1972,6 +2702,20 @@
       <c r="W43" s="5" t="n"/>
       <c r="X43" s="5" t="n"/>
       <c r="Y43" s="5" t="n"/>
+      <c r="Z43" s="5" t="n"/>
+      <c r="AA43" s="5" t="n"/>
+      <c r="AB43" s="5" t="n"/>
+      <c r="AC43" s="5" t="n"/>
+      <c r="AD43" s="5" t="n"/>
+      <c r="AE43" s="5" t="n"/>
+      <c r="AF43" s="5" t="n"/>
+      <c r="AG43" s="5" t="n"/>
+      <c r="AH43" s="5" t="n"/>
+      <c r="AI43" s="5" t="n"/>
+      <c r="AJ43" s="5" t="n"/>
+      <c r="AK43" s="5" t="n"/>
+      <c r="AL43" s="5" t="n"/>
+      <c r="AM43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1999,6 +2743,20 @@
       <c r="W44" s="5" t="n"/>
       <c r="X44" s="5" t="n"/>
       <c r="Y44" s="5" t="n"/>
+      <c r="Z44" s="5" t="n"/>
+      <c r="AA44" s="5" t="n"/>
+      <c r="AB44" s="5" t="n"/>
+      <c r="AC44" s="5" t="n"/>
+      <c r="AD44" s="5" t="n"/>
+      <c r="AE44" s="5" t="n"/>
+      <c r="AF44" s="5" t="n"/>
+      <c r="AG44" s="5" t="n"/>
+      <c r="AH44" s="5" t="n"/>
+      <c r="AI44" s="5" t="n"/>
+      <c r="AJ44" s="5" t="n"/>
+      <c r="AK44" s="5" t="n"/>
+      <c r="AL44" s="5" t="n"/>
+      <c r="AM44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -2026,6 +2784,20 @@
       <c r="W45" s="5" t="n"/>
       <c r="X45" s="5" t="n"/>
       <c r="Y45" s="5" t="n"/>
+      <c r="Z45" s="5" t="n"/>
+      <c r="AA45" s="5" t="n"/>
+      <c r="AB45" s="5" t="n"/>
+      <c r="AC45" s="5" t="n"/>
+      <c r="AD45" s="5" t="n"/>
+      <c r="AE45" s="5" t="n"/>
+      <c r="AF45" s="5" t="n"/>
+      <c r="AG45" s="5" t="n"/>
+      <c r="AH45" s="5" t="n"/>
+      <c r="AI45" s="5" t="n"/>
+      <c r="AJ45" s="5" t="n"/>
+      <c r="AK45" s="5" t="n"/>
+      <c r="AL45" s="5" t="n"/>
+      <c r="AM45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -2053,6 +2825,20 @@
       <c r="W46" s="5" t="n"/>
       <c r="X46" s="5" t="n"/>
       <c r="Y46" s="5" t="n"/>
+      <c r="Z46" s="5" t="n"/>
+      <c r="AA46" s="5" t="n"/>
+      <c r="AB46" s="5" t="n"/>
+      <c r="AC46" s="5" t="n"/>
+      <c r="AD46" s="5" t="n"/>
+      <c r="AE46" s="5" t="n"/>
+      <c r="AF46" s="5" t="n"/>
+      <c r="AG46" s="5" t="n"/>
+      <c r="AH46" s="5" t="n"/>
+      <c r="AI46" s="5" t="n"/>
+      <c r="AJ46" s="5" t="n"/>
+      <c r="AK46" s="5" t="n"/>
+      <c r="AL46" s="5" t="n"/>
+      <c r="AM46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -2080,6 +2866,20 @@
       <c r="W47" s="5" t="n"/>
       <c r="X47" s="5" t="n"/>
       <c r="Y47" s="5" t="n"/>
+      <c r="Z47" s="5" t="n"/>
+      <c r="AA47" s="5" t="n"/>
+      <c r="AB47" s="5" t="n"/>
+      <c r="AC47" s="5" t="n"/>
+      <c r="AD47" s="5" t="n"/>
+      <c r="AE47" s="5" t="n"/>
+      <c r="AF47" s="5" t="n"/>
+      <c r="AG47" s="5" t="n"/>
+      <c r="AH47" s="5" t="n"/>
+      <c r="AI47" s="5" t="n"/>
+      <c r="AJ47" s="5" t="n"/>
+      <c r="AK47" s="5" t="n"/>
+      <c r="AL47" s="5" t="n"/>
+      <c r="AM47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -2107,6 +2907,20 @@
       <c r="W48" s="5" t="n"/>
       <c r="X48" s="5" t="n"/>
       <c r="Y48" s="5" t="n"/>
+      <c r="Z48" s="5" t="n"/>
+      <c r="AA48" s="5" t="n"/>
+      <c r="AB48" s="5" t="n"/>
+      <c r="AC48" s="5" t="n"/>
+      <c r="AD48" s="5" t="n"/>
+      <c r="AE48" s="5" t="n"/>
+      <c r="AF48" s="5" t="n"/>
+      <c r="AG48" s="5" t="n"/>
+      <c r="AH48" s="5" t="n"/>
+      <c r="AI48" s="5" t="n"/>
+      <c r="AJ48" s="5" t="n"/>
+      <c r="AK48" s="5" t="n"/>
+      <c r="AL48" s="5" t="n"/>
+      <c r="AM48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -2134,6 +2948,20 @@
       <c r="W49" s="5" t="n"/>
       <c r="X49" s="5" t="n"/>
       <c r="Y49" s="5" t="n"/>
+      <c r="Z49" s="5" t="n"/>
+      <c r="AA49" s="5" t="n"/>
+      <c r="AB49" s="5" t="n"/>
+      <c r="AC49" s="5" t="n"/>
+      <c r="AD49" s="5" t="n"/>
+      <c r="AE49" s="5" t="n"/>
+      <c r="AF49" s="5" t="n"/>
+      <c r="AG49" s="5" t="n"/>
+      <c r="AH49" s="5" t="n"/>
+      <c r="AI49" s="5" t="n"/>
+      <c r="AJ49" s="5" t="n"/>
+      <c r="AK49" s="5" t="n"/>
+      <c r="AL49" s="5" t="n"/>
+      <c r="AM49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -2161,6 +2989,20 @@
       <c r="W50" s="5" t="n"/>
       <c r="X50" s="5" t="n"/>
       <c r="Y50" s="5" t="n"/>
+      <c r="Z50" s="5" t="n"/>
+      <c r="AA50" s="5" t="n"/>
+      <c r="AB50" s="5" t="n"/>
+      <c r="AC50" s="5" t="n"/>
+      <c r="AD50" s="5" t="n"/>
+      <c r="AE50" s="5" t="n"/>
+      <c r="AF50" s="5" t="n"/>
+      <c r="AG50" s="5" t="n"/>
+      <c r="AH50" s="5" t="n"/>
+      <c r="AI50" s="5" t="n"/>
+      <c r="AJ50" s="5" t="n"/>
+      <c r="AK50" s="5" t="n"/>
+      <c r="AL50" s="5" t="n"/>
+      <c r="AM50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -2188,6 +3030,20 @@
       <c r="W51" s="5" t="n"/>
       <c r="X51" s="5" t="n"/>
       <c r="Y51" s="5" t="n"/>
+      <c r="Z51" s="5" t="n"/>
+      <c r="AA51" s="5" t="n"/>
+      <c r="AB51" s="5" t="n"/>
+      <c r="AC51" s="5" t="n"/>
+      <c r="AD51" s="5" t="n"/>
+      <c r="AE51" s="5" t="n"/>
+      <c r="AF51" s="5" t="n"/>
+      <c r="AG51" s="5" t="n"/>
+      <c r="AH51" s="5" t="n"/>
+      <c r="AI51" s="5" t="n"/>
+      <c r="AJ51" s="5" t="n"/>
+      <c r="AK51" s="5" t="n"/>
+      <c r="AL51" s="5" t="n"/>
+      <c r="AM51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -2215,6 +3071,20 @@
       <c r="W52" s="5" t="n"/>
       <c r="X52" s="5" t="n"/>
       <c r="Y52" s="5" t="n"/>
+      <c r="Z52" s="5" t="n"/>
+      <c r="AA52" s="5" t="n"/>
+      <c r="AB52" s="5" t="n"/>
+      <c r="AC52" s="5" t="n"/>
+      <c r="AD52" s="5" t="n"/>
+      <c r="AE52" s="5" t="n"/>
+      <c r="AF52" s="5" t="n"/>
+      <c r="AG52" s="5" t="n"/>
+      <c r="AH52" s="5" t="n"/>
+      <c r="AI52" s="5" t="n"/>
+      <c r="AJ52" s="5" t="n"/>
+      <c r="AK52" s="5" t="n"/>
+      <c r="AL52" s="5" t="n"/>
+      <c r="AM52" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2227,17 +3097,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>📋 픽스카 매물 일괄등록 양식 가이드</t>
+          <t>📋 픽스카 매물 일괄등록 양식 v3</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -2247,102 +3117,74 @@
       <c r="B2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>* 표시 항목은 필수 입력입니다.</t>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>■ 기본 규칙</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>2행은 입력 가이드입니다. 삭제하지 마세요.</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr"/>
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>* 표시 항목은 필수 입력</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>3행은 예시 데이터입니다. 수정/삭제 후 사용하세요.</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2행은 입력 가이드 (삭제 금지)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>3행은 예시 데이터 (수정/삭제 후 사용)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>▶ 연료</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>가솔린, 디젤, LPG, 하이브리드, 전기 중 택1</t>
-        </is>
-      </c>
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>▶ 변속기</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>오토, 수동, 세미오토, CVT, 기타 중 택1</t>
-        </is>
-      </c>
+          <t>■ 필수 항목 (7개)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>▶ 사고여부</t>
-        </is>
-      </c>
+      <c r="A9" s="7" t="inlineStr"/>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>무사고 또는 있음</t>
+          <t>브랜드, 모델명, 연식, 주행거리, 연료, 사고여부, 판매가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>▶ 판매구분</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>일반차량, 리스승계, 렌트 중 택1</t>
-        </is>
-      </c>
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>▶ 옵션</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>콤마(,)로 구분하여 입력. 예: 선루프,후방카메라,열선시트</t>
-        </is>
-      </c>
+          <t>■ 사진은 업로드 후 관리자 페이지에서 수기 등록</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>▶ 사진 URL</t>
-        </is>
-      </c>
+      <c r="A12" s="7" t="inlineStr"/>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Cloudinary에 업로드된 이미지 URL. 비워두면 사진 없음.</t>
+          <t>엑셀에는 사진 URL 없음</t>
         </is>
       </c>
     </row>
@@ -2351,12 +3193,140 @@
       <c r="B13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>문의: info@fixcar.kr</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>■ 연료</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>가솔린, 디젤, LPG, 하이브리드, 전기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>■ 변속기</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>오토, 수동, 세미오토, CVT, 기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>■ 사고여부</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>무사고 또는 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>■ 판매구분</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>일반차량(기본), 리스승계차량, 렌트차량</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>■ 매매유형</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>직접매도(기본), 매매알선</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>■ 압류/저당</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>없음(기본) 또는 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>■ 사고이력공개</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>공개 또는 비공개(기본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>■ 옵션</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>콤마(,)로 구분. 예: 선루프,후방카메라,열선시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>■ 리스/렌트</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>판매구분이 리스승계/렌트인 경우에만 Y~AM열 작성</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>일반차량은 비워두세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>■ 등록 상태</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>모든 매물은 '검수대기' → 사진 등록 후 승인</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
